--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_314_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_314_R32.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7678</v>
+        <v>1.9373</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1993</v>
+        <v>1.592</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5685</v>
+        <v>0.3452</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4272</v>
+        <v>2.6577</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.222</v>
+        <v>0.2787</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6492</v>
+        <v>2.379</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6956</v>
+        <v>3.2941</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1141</v>
+        <v>0.3865</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8097</v>
+        <v>2.9076</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2683</v>
+        <v>-0.6364</v>
       </c>
       <c r="N2" t="n">
         <v>-0.1078</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1605</v>
+        <v>-0.5286</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="R2" t="n">
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4128</v>
+        <v>-0.4885</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8259</v>
+        <v>-0.0784</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5869</v>
+        <v>-0.4101</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.805</v>
+        <v>1.7225</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5606</v>
+        <v>0.7589</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2444</v>
+        <v>0.9636</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6577</v>
+        <v>0.4272</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2787</v>
+        <v>-0.222</v>
       </c>
       <c r="I3" t="n">
-        <v>2.379</v>
+        <v>0.6492</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2941</v>
+        <v>0.6956</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3865</v>
+        <v>-0.1141</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9076</v>
+        <v>0.8097</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6364</v>
+        <v>-0.2683</v>
       </c>
       <c r="N3" t="n">
         <v>-0.1078</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5286</v>
+        <v>-0.1605</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="R3" t="n">
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6207</v>
+        <v>0.3675</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1098</v>
+        <v>0.3855</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5109</v>
+        <v>-0.018</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.178</v>
+        <v>1.5639</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9004</v>
+        <v>1.4033</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7224</v>
+        <v>0.1606</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.325</v>
+        <v>-2.0316</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2112</v>
+        <v>-1.7303</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1138</v>
+        <v>-0.3013</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2367</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2283</v>
+        <v>-1.0644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.465</v>
+        <v>0.2272</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5617</v>
+        <v>-1.1944</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0171</v>
+        <v>-0.6659</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5788</v>
+        <v>-0.5286</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.9405</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0553</v>
+        <v>0.0239</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7121</v>
+        <v>-0.9645</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>2.6805</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3937</v>
+        <v>1.4133</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1883</v>
+        <v>1.9004</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2054</v>
+        <v>-0.4871</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6765</v>
+        <v>-0.325</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2353</v>
+        <v>-0.2112</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5589</v>
+        <v>-0.1138</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1579</v>
+        <v>0.2367</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1947</v>
+        <v>-0.2283</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>0.465</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.5617</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0406</v>
+        <v>0.0171</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5221</v>
+        <v>-0.5788</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3743</v>
+        <v>-0.4215</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3462</v>
+        <v>0.0553</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0281</v>
+        <v>-0.4769</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3829</v>
+        <v>0.0233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3697</v>
+        <v>-0.0476</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0133</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5498</v>
+        <v>-0.6765</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4093</v>
+        <v>-1.2353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1404</v>
+        <v>0.5589</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6554</v>
+        <v>-0.1579</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5818</v>
+        <v>-0.1947</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2052</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9912</v>
+        <v>-1.0406</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.214</v>
+        <v>0.5221</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8089</v>
+        <v>0.004</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9099</v>
+        <v>0.1103</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.101</v>
+        <v>-0.1063</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2522</v>
+        <v>-0.2957</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1924</v>
+        <v>-1.0108</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0598</v>
+        <v>0.7151</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0316</v>
+        <v>-1.1627</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7303</v>
+        <v>-3.5785</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3013</v>
+        <v>2.4158</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0644</v>
+        <v>-3.2595</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2272</v>
+        <v>2.9444</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1944</v>
+        <v>-0.8476</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6659</v>
+        <v>-0.319</v>
       </c>
       <c r="O7" t="n">
         <v>-0.5286</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2523</v>
+        <v>-1.151</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.187</v>
+        <v>-0.2317</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0653</v>
+        <v>-0.9192</v>
       </c>
       <c r="V7" t="n">
-        <v>2.6805</v>
+        <v>0.3943</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5256</v>
+        <v>-0.427</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4306</v>
+        <v>-0.3992</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.095</v>
+        <v>-0.0278</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4211</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3365</v>
+        <v>-0.2379</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0395</v>
+        <v>0.0709</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.376</v>
+        <v>-0.3088</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3373</v>
+        <v>-1.0771</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7499</v>
+        <v>-0.78</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4126</v>
+        <v>-0.2971</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1627</v>
+        <v>-0.9485</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.5785</v>
+        <v>0.293</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4158</v>
+        <v>-1.2414</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3151</v>
+        <v>-0.8195</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.2595</v>
+        <v>0.0539</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9444</v>
+        <v>-0.8734</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8476</v>
+        <v>-0.129</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.319</v>
+        <v>0.2391</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5286</v>
+        <v>-0.368</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1925</v>
+        <v>0.0158</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9709</v>
+        <v>0.0395</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2217</v>
+        <v>-0.0237</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5489</v>
+        <v>-1.4584</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2518</v>
+        <v>-1.897</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2971</v>
+        <v>0.4386</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9485</v>
+        <v>-1.2273</v>
       </c>
       <c r="H10" t="n">
-        <v>0.293</v>
+        <v>-1.6891</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2414</v>
+        <v>0.4618</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8195</v>
+        <v>-0.9697</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0539</v>
+        <v>-1.4348</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8734</v>
+        <v>0.465</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.129</v>
+        <v>-0.2576</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2391</v>
+        <v>-0.2543</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.368</v>
+        <v>-0.0033</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.456</v>
+        <v>0.1632</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4323</v>
+        <v>0.0907</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0237</v>
+        <v>0.0725</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8465</v>
+        <v>-2.0091</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4868</v>
+        <v>-1.7535</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6402</v>
+        <v>-0.2556</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2273</v>
+        <v>-0.5498</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6891</v>
+        <v>-0.4093</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4618</v>
+        <v>-0.1404</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9697</v>
+        <v>0.6554</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4348</v>
+        <v>0.5818</v>
       </c>
       <c r="L11" t="n">
-        <v>0.465</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2576</v>
+        <v>-1.2052</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2543</v>
+        <v>-0.9912</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0033</v>
+        <v>-0.214</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2249</v>
+        <v>0.4169</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4991</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2741</v>
+        <v>-0.3699</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3943</v>
+        <v>-0.2525</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>0.2836</v>
       </c>
       <c r="X11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3424</v>
+        <v>-4.3767</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6167</v>
+        <v>-2.8527</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7257</v>
+        <v>-1.524</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4363</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5298</v>
+        <v>-0.5641</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1221</v>
+        <v>-0.1138</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6519</v>
+        <v>-0.4503</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7379</v>
+        <v>-6.8285</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2915</v>
+        <v>-5.5838</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4464</v>
+        <v>-1.2448</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6924</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4734</v>
+        <v>-0.5641</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8804</v>
+        <v>-0.1727</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.593</v>
+        <v>-0.3914</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3247</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.559</v>
+        <v>-9.812200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.416599999999999</v>
+        <v>-8.67</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1424</v>
+        <v>-1.1423</v>
       </c>
       <c r="G14" t="n">
         <v>-9.3863</v>
@@ -1519,10 +1519,10 @@
         <v>2.1081</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.0184</v>
+        <v>-2.018400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.999000000000001</v>
+        <v>-5.999</v>
       </c>
       <c r="L14" t="n">
         <v>3.980699999999999</v>
@@ -1546,13 +1546,13 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.1469</v>
+        <v>-3.4002</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2193999999999999</v>
+        <v>0.9663000000000003</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.3665</v>
+        <v>-4.3666</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5050000000000003</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4712</v>
+        <v>4.8244</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>4.1179</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4712</v>
+        <v>0.7065</v>
       </c>
       <c r="G15" t="n">
         <v>4.5851</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.4353</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2794</v>
+        <v>0.3973</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1972</v>
+        <v>0.038</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3558</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8857</v>
+        <v>4.1894</v>
       </c>
       <c r="E16" t="n">
         <v>3.1628</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7228</v>
+        <v>1.0266</v>
       </c>
       <c r="G16" t="n">
         <v>2.7637</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6427</v>
+        <v>0.9465</v>
       </c>
       <c r="T16" t="n">
         <v>0.6844</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0417</v>
+        <v>0.2621</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2596</v>
+        <v>3.4289</v>
       </c>
       <c r="E17" t="n">
         <v>1.0791</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1805</v>
+        <v>2.3498</v>
       </c>
       <c r="G17" t="n">
         <v>4.1165</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9265</v>
+        <v>1.0958</v>
       </c>
       <c r="T17" t="n">
         <v>0.6844</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2421</v>
+        <v>0.4114</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1801</v>
+        <v>2.2372</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3368</v>
+        <v>-0.371</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8434</v>
+        <v>2.6081</v>
       </c>
       <c r="G18" t="n">
         <v>1.3373</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5361</v>
+        <v>1.5931</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7774</v>
+        <v>1.0697</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7587</v>
+        <v>0.5234</v>
       </c>
       <c r="V18" t="n">
         <v>0.9304</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5878</v>
+        <v>1.5929</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6044</v>
+        <v>1.2506</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0166</v>
+        <v>0.3423</v>
       </c>
       <c r="G19" t="n">
         <v>2.1285</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2996</v>
+        <v>0.3047</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.2243</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2785</v>
+        <v>0.0804</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.9476</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2158</v>
+        <v>-0.6047</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9996</v>
+        <v>1.5523</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1187</v>
+        <v>-0.3707</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6614</v>
+        <v>0.3887</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7801</v>
+        <v>-0.7595</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2503</v>
+        <v>-0.224</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1078</v>
+        <v>-0.1002</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3581</v>
+        <v>-0.1239</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8683</v>
+        <v>-0.1467</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5536</v>
+        <v>0.4889</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.422</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8303</v>
+        <v>0.6379</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1221</v>
+        <v>0.5625</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2183</v>
+        <v>0.7361</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3098</v>
+        <v>-0.838</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0914</v>
+        <v>1.574</v>
       </c>
       <c r="G21" t="n">
         <v>-0.789</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8237</v>
+        <v>0.1307</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3655</v>
+        <v>0.1063</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4582</v>
+        <v>0.0244</v>
       </c>
       <c r="V21" t="n">
         <v>0.9304</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.282</v>
+        <v>0.6494</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1944</v>
+        <v>-0.2158</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9125</v>
+        <v>0.8651</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3707</v>
+        <v>-1.1187</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3887</v>
+        <v>0.6614</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7595</v>
+        <v>-1.7801</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.224</v>
+        <v>-0.2503</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1002</v>
+        <v>0.1078</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1239</v>
+        <v>-0.3581</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1467</v>
+        <v>-0.8683</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4889</v>
+        <v>0.5536</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.422</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5917</v>
+        <v>0.6959</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0272</v>
+        <v>0.1221</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5645</v>
+        <v>0.5737</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3794</v>
+        <v>-0.3953</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7238</v>
+        <v>-0.3699</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3443</v>
+        <v>-0.0253</v>
       </c>
       <c r="G23" t="n">
         <v>0.5331</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5513</v>
+        <v>0.5355</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2829</v>
+        <v>0.0709</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.4646</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6771</v>
+        <v>-2.3575</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1576</v>
+        <v>-2.0397</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5195</v>
+        <v>-0.3178</v>
       </c>
       <c r="G24" t="n">
         <v>-0.724</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7934</v>
+        <v>-0.4738</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0524</v>
+        <v>-2.9351</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5811</v>
+        <v>-4.1709</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5286999999999999</v>
+        <v>1.2357</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0757</v>
@@ -2404,13 +2404,13 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4872</v>
+        <v>0.6045</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2151</v>
+        <v>0.6253</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7279</v>
+        <v>-0.0209</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.559</v>
+        <v>12.918</v>
       </c>
       <c r="E26" t="n">
-        <v>1.000599999999999</v>
+        <v>1.0004</v>
       </c>
       <c r="F26" t="n">
-        <v>9.558299999999999</v>
+        <v>11.9173</v>
       </c>
       <c r="G26" t="n">
         <v>9.386099999999999</v>
@@ -2482,19 +2482,19 @@
         <v>12.7575</v>
       </c>
       <c r="S26" t="n">
-        <v>4.147</v>
+        <v>6.5061</v>
       </c>
       <c r="T26" t="n">
-        <v>4.3666</v>
+        <v>4.3664</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2193999999999996</v>
+        <v>2.1394</v>
       </c>
       <c r="V26" t="n">
-        <v>0.5049999999999997</v>
+        <v>0.5050000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>5.502800000000001</v>
+        <v>5.5028</v>
       </c>
       <c r="X26" t="n">
         <v>-4.997800000000001</v>
